--- a/reports/tables/fv_calibration_threshold.xlsx
+++ b/reports/tables/fv_calibration_threshold.xlsx
@@ -442,7 +442,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.06428571428571428</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
